--- a/out/MLP-Mamba1_repeat_5_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.815552302146114</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.415552302146114</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.415552302146114</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.415552302146114</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.415552302146114</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.415552302146114</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.415552302146114</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003789665635067504</v>
+        <v>-0.000251428402582882</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1631718922886682</v>
+        <v>0.1082576631266132</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.415552302146114</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3267794621874811</v>
+        <v>0.2168044523045868</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6304201412757895</v>
+        <v>0.4182574324535989</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.415552302146114</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.424864911152109</v>
+        <v>0.9453382830434758</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1939202603982264</v>
+        <v>0.1286578218415317</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.181488251134194</v>
+        <v>0.7838680348202363</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03934806990405273</v>
+        <v>0.02610562909198576</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.815552302146114</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.065959741186905</v>
+        <v>0.7072195924754462</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03407717727874076</v>
+        <v>0.0226086350031879</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.094722526019766</v>
+        <v>0.726302676167306</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01665955857814107</v>
+        <v>0.01105319837123483</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.815552302146114</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.09392050941859</v>
+        <v>0.7257705583114666</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.007949583030231218</v>
+        <v>0.005272887556135774</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.093139639645129</v>
+        <v>0.7252507877540654</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003309095838701111</v>
+        <v>0.002193448591807607</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.815552302146114</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.091798446801872</v>
+        <v>0.724359295251969</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002291494354317739</v>
+        <v>0.001519051192801591</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.093070111359759</v>
+        <v>0.7252014012476734</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0009536990912125865</v>
+        <v>0.0006309112923567358</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>3.415552302146114</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.092683391206416</v>
+        <v>0.7249431608661933</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004921196786637569</v>
+        <v>0.0003250767758869569</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.092712956244605</v>
+        <v>0.7249610954303104</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001902494401594864</v>
+        <v>0.0001246414293532074</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.092600606996837</v>
+        <v>0.7248849131058143</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001015097866084753</v>
+        <v>6.543389114431433e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.092613207195828</v>
+        <v>0.7248915681464032</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.751447109351001e-05</v>
+        <v>3.000964739567334e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.092606597935532</v>
+        <v>0.7248855006202685</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.004280393309856e-05</v>
+        <v>1.151759408353309e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.09259854263149</v>
+        <v>0.7248784854197304</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.606952625195229e-06</v>
+        <v>1.917577799040367e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.092590144371147</v>
+        <v>0.7248712442099938</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.91678593955831e-08</v>
+        <v>-1.69277857293039e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.092583983402742</v>
+        <v>0.724865470231057</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.09281402832566e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.092577829688441</v>
+        <v>0.7248597010881894</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.634963333793937e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.092572014186287</v>
+        <v>0.7248541574200869</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.092567132888038</v>
+        <v>0.7248492362663655</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.09256221168649</v>
+        <v>0.7248492761218378</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.415552302146114</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.092562203715395</v>
+        <v>0.7248492681507434</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.092562363137284</v>
+        <v>0.7248494275726325</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.415552302146114</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.092562267484151</v>
+        <v>0.724849331919499</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.092562618212307</v>
+        <v>0.7248496826476553</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.092562371108379</v>
+        <v>0.7248494355437269</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.092562331252907</v>
+        <v>0.7248493956882546</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.092562267484151</v>
+        <v>0.724849331919499</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.092562339224001</v>
+        <v>0.724849403659349</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.092562267484151</v>
+        <v>0.724849331919499</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.415552302146114</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.092562371108379</v>
+        <v>0.7248494355437269</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.092562466761513</v>
+        <v>0.7248495311968606</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.092562402992757</v>
+        <v>0.7248494674281047</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.092562363137284</v>
+        <v>0.7248494275726325</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.092562339224001</v>
+        <v>0.724849403659349</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.092562092120073</v>
+        <v>0.7248491565554209</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.092562012409128</v>
+        <v>0.7248490768444762</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.092562060235695</v>
+        <v>0.7248491246710429</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.092562179802112</v>
+        <v>0.72484924423746</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.092562163859923</v>
+        <v>0.7248492282952711</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.092562179802112</v>
+        <v>0.72484924423746</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.092562163859923</v>
+        <v>0.7248492282952711</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.092562219657584</v>
+        <v>0.7248492840929323</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.092562219657584</v>
+        <v>0.7248492840929323</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.415552302146114</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.092562219657584</v>
+        <v>0.7248492840929323</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.092562371108379</v>
+        <v>0.7248494355437269</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.09256258632793</v>
+        <v>0.7248496507632775</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.092562498645891</v>
+        <v>0.7248495630812384</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.092562450819324</v>
+        <v>0.7248495152546717</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.092562498645891</v>
+        <v>0.7248495630812384</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.092562315310718</v>
+        <v>0.7248493797460657</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.092562323281812</v>
+        <v>0.7248493877171601</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.092562331252907</v>
+        <v>0.7248493956882546</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.092562339224001</v>
+        <v>0.724849403659349</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.092562339224001</v>
+        <v>0.724849403659349</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>3.415552302146114</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.092562379079473</v>
+        <v>0.7248494435148214</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>3.415552302146114</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.092562442848229</v>
+        <v>0.7248495072835772</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.092562554443552</v>
+        <v>0.7248496188788996</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.092562602270118</v>
+        <v>0.7248496667054664</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.092562562414646</v>
+        <v>0.7248496268499941</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>3.415552302146114</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.092562490674796</v>
+        <v>0.7248495551101439</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.092562610241213</v>
+        <v>0.7248496746765608</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.092562450819324</v>
+        <v>0.7248495152546717</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.092562219657584</v>
+        <v>0.7248492840929323</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.092562171831018</v>
+        <v>0.7248492362663655</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.092562203715395</v>
+        <v>0.7248492681507434</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.092562267484151</v>
+        <v>0.724849331919499</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.092562267484151</v>
+        <v>0.724849331919499</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.092562187773207</v>
+        <v>0.7248492522085545</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.092562068206789</v>
+        <v>0.7248491326421374</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.092562028351317</v>
+        <v>0.7248490927866651</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.092562171831018</v>
+        <v>0.7248492362663655</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.092562307339623</v>
+        <v>0.7248493717749712</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.092562291397434</v>
+        <v>0.7248493558327823</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.092562267484151</v>
+        <v>0.724849331919499</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.092562227628679</v>
+        <v>0.7248492920640267</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.092562124004451</v>
+        <v>0.7248491884397987</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>3.415552302146114</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.092562004438034</v>
+        <v>0.7248490688733817</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.092562124004451</v>
+        <v>0.7248491884397987</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.092562171831018</v>
+        <v>0.7248492362663655</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.092562267484151</v>
+        <v>0.724849331919499</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.092562147917734</v>
+        <v>0.7248492123530822</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.092562155888829</v>
+        <v>0.7248492203241766</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_5_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.8124972782795411</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.815552302146114</v>
+        <v>0.3845367972155144</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3291019071641193</v>
+        <v>0.5845367972155144</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-0.2713841649125389</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.415552302146114</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3291019071641193</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-0.2713841649125389</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.2713841649125389</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.415552302146114</v>
+        <v>1.440457759343568</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.415552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.415552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.415552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.415552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003789665635067504</v>
+        <v>-0.0002875576993708965</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1631718922886682</v>
+        <v>0.12381399642403</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.415552302146114</v>
+        <v>2.296378721471621</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3267794621874811</v>
+        <v>0.2479584196691622</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.6304201412757895</v>
+        <v>0.478358120244495</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.415552302146114</v>
+        <v>1.440457759343568</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.424864911152109</v>
+        <v>1.081178944193657</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1939202603982264</v>
+        <v>0.1471461483367371</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.440457759343568</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.181488251134194</v>
+        <v>0.8965059027595849</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03934806990405273</v>
+        <v>0.02985684150146876</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.815552302146114</v>
+        <v>0.3845367972155144</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.065959741186905</v>
+        <v>0.8088436551323475</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03407717727874076</v>
+        <v>0.02585735166451004</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.240457759343568</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.094722526019766</v>
+        <v>0.8306688127215908</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01665955857814107</v>
+        <v>0.01264142221619642</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.815552302146114</v>
+        <v>0.3845367972155144</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.09392050941859</v>
+        <v>0.8300602353434856</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.007949583030231218</v>
+        <v>0.006031262334742447</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.240457759343568</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.093139639645129</v>
+        <v>0.8294664978810772</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003309095838701111</v>
+        <v>0.002509659987134709</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.815552302146114</v>
+        <v>0.3845367972155144</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.091798446801872</v>
+        <v>0.8284476253675556</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002291494354317739</v>
+        <v>0.001737434224478984</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9291019071641193</v>
+        <v>1.240457759343568</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.093070111359759</v>
+        <v>0.8294113293659923</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0009536990912125865</v>
+        <v>0.0007224000497170767</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>3.415552302146114</v>
+        <v>0.3845367972155144</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.092683391206416</v>
+        <v>0.8291166735601518</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004921196786637569</v>
+        <v>0.0003725169602755681</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.3845367972155144</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.092712956244605</v>
+        <v>0.8291379043875328</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001902494401594864</v>
+        <v>0.0001430116723789656</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.092600606996837</v>
+        <v>0.8290514920191364</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001015097866084753</v>
+        <v>7.574128984836033e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.092613207195828</v>
+        <v>0.8290598456764119</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.751447109351001e-05</v>
+        <v>3.509169298536786e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.092606597935532</v>
+        <v>0.829053623186806</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.004280393309856e-05</v>
+        <v>1.364889654592446e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.09259854263149</v>
+        <v>0.829046316076014</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.606952625195229e-06</v>
+        <v>3.301093358848441e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.092590144371147</v>
+        <v>0.8290387127121503</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.91678593955831e-08</v>
+        <v>-1.279375894546688e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.092583983402742</v>
+        <v>0.8290328419858461</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.09281402832566e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.092577829688441</v>
+        <v>0.829026977189845</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.634963333793937e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.092572014186287</v>
+        <v>0.8290212980131367</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.092567132888038</v>
+        <v>0.8290164167148873</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.09256221168649</v>
+        <v>0.8290114955133395</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.415552302146114</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.092562203715395</v>
+        <v>0.8290114875422451</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3291019071641193</v>
+        <v>1.440457759343568</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.092562363137284</v>
+        <v>0.8290116469641342</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.415552302146114</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.092562267484151</v>
+        <v>0.8290115513110007</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3291019071641193</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.092562618212307</v>
+        <v>0.829011902039157</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-0.2713841649125389</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.092562371108379</v>
+        <v>0.8290116549352287</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.092562331252907</v>
+        <v>0.8290116150797564</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.092562267484151</v>
+        <v>0.8290115513110007</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.092562339224001</v>
+        <v>0.8290116230508509</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.3845367972155147</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.092562267484151</v>
+        <v>0.8290115513110007</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.415552302146114</v>
+        <v>0.3845367972155147</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.092562371108379</v>
+        <v>0.8290116549352287</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3291019071641193</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.092562466761513</v>
+        <v>0.8290117505883623</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-0.2713841649125389</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.092562402992757</v>
+        <v>0.8290116868196065</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.092562363137284</v>
+        <v>0.8290116469641342</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.092562339224001</v>
+        <v>0.8290116230508509</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.092562092120073</v>
+        <v>0.8290113759469226</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.092562012409128</v>
+        <v>0.8290112962359779</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.092562060235695</v>
+        <v>0.8290113440625446</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.092562179802112</v>
+        <v>0.8290114636289617</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.092562163859923</v>
+        <v>0.8290114476867728</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.092562179802112</v>
+        <v>0.8290114636289617</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.092562163859923</v>
+        <v>0.8290114476867728</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.092562219657584</v>
+        <v>0.829011503484434</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.092562219657584</v>
+        <v>0.829011503484434</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.415552302146114</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.092562219657584</v>
+        <v>0.829011503484434</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3291019071641193</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.092562371108379</v>
+        <v>0.8290116549352287</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-0.2713841649125389</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.09256258632793</v>
+        <v>0.8290118701547792</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.2713841649125389</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.092562498645891</v>
+        <v>0.8290117824727402</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.092562450819324</v>
+        <v>0.8290117346461734</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.092562498645891</v>
+        <v>0.8290117824727402</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.092562315310718</v>
+        <v>0.8290115991375675</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.092562323281812</v>
+        <v>0.829011607108662</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.092562331252907</v>
+        <v>0.8290116150797564</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.092562339224001</v>
+        <v>0.8290116230508509</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.092562339224001</v>
+        <v>0.8290116230508509</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>3.415552302146114</v>
+        <v>1.440457759343568</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.092562379079473</v>
+        <v>0.8290116629063231</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>3.415552302146114</v>
+        <v>1.440457759343568</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.092562442848229</v>
+        <v>0.8290117266750789</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3291019071641193</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.092562554443552</v>
+        <v>0.8290118382704014</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-0.2713841649125389</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.092562602270118</v>
+        <v>0.8290118860969681</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.3845367972155147</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.092562562414646</v>
+        <v>0.8290118462414958</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>3.415552302146114</v>
+        <v>0.3845367972155147</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.092562490674796</v>
+        <v>0.8290117745016458</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3291019071641193</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.092562610241213</v>
+        <v>0.8290118940680625</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.092562450819324</v>
+        <v>0.8290117346461734</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.092562219657584</v>
+        <v>0.829011503484434</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.092562171831018</v>
+        <v>0.8290114556578673</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.092562203715395</v>
+        <v>0.8290114875422451</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.092562267484151</v>
+        <v>0.8290115513110007</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.092562267484151</v>
+        <v>0.8290115513110007</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.092562187773207</v>
+        <v>0.8290114716000562</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.092562068206789</v>
+        <v>0.8290113520336391</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.092562028351317</v>
+        <v>0.8290113121781668</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.092562171831018</v>
+        <v>0.8290114556578673</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.092562307339623</v>
+        <v>0.8290115911664729</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.092562291397434</v>
+        <v>0.829011575224284</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.092562267484151</v>
+        <v>0.8290115513110007</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.092562227628679</v>
+        <v>0.8290115114555284</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9291019071641193</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.092562124004451</v>
+        <v>0.8290114078313006</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>3.415552302146114</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.092562004438034</v>
+        <v>0.8290112882648835</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3291019071641193</v>
+        <v>0.5845367972155147</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.092562124004451</v>
+        <v>0.8290114078313006</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3291019071641193</v>
+        <v>-0.2713841649125389</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.092562171831018</v>
+        <v>0.8290114556578673</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.2713841649125389</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.092562267484151</v>
+        <v>0.8290115513110007</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.092562147917734</v>
+        <v>0.8290114317445839</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9291019071641193</v>
+        <v>-0.471384164912539</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.092562155888829</v>
+        <v>0.8290114397156784</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_5_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4385131001472473</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.8124972782795411</v>
+        <v>0.1199999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5078768134117126</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.3845367972155144</v>
+        <v>-0.1600000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4364888072013855</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5845367972155144</v>
+        <v>0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.3935190737247467</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.2713841649125389</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4154058992862701</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4158584177494049</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4181393384933472</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4270336031913757</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4721526801586151</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.3974392116069794</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.391247570514679</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.16</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4019472897052765</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4758819937705994</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.484271228313446</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.5845367972155147</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.5183424353599548</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.5845367972155147</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.476141095161438</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.5845367972155147</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4161631762981415</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.2713841649125389</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4346599280834198</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.2713841649125389</v>
+        <v>0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4481705129146576</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.3911847472190857</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3592920303344727</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.3486513793468475</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3325609266757965</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4569401741027832</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3930076360702515</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3814736306667328</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3849523961544037</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4088797867298126</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4280325770378113</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.3683603405952454</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4205145835876465</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.310472697019577</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4480330944061279</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.386787474155426</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4178036749362946</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4168274104595184</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4596005082130432</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.5845367972155147</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5028281211853027</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.440457759343568</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.6043159961700439</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.296378721471621</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5494162440299988</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.296378721471621</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.8017293214797974</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.296378721471621</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6798956990242004</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.296378721471621</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002875576993708965</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.12381399642403</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.8936231136322021</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.296378721471621</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2479584196691622</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.478358120244495</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.7971402406692505</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.440457759343568</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.081178944193657</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1471461483367371</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.1578812301158905</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.440457759343568</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.8965059027595849</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02985684150146876</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.7257635593414307</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.3845367972155144</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8088436551323475</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02585735166451004</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.3386078178882599</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.240457759343568</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.8306688127215908</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01264142221619642</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.5591912269592285</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.3845367972155144</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8300602353434856</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006031262334742447</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4408299624919891</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.240457759343568</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8294664978810772</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002509659987134709</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5545339584350586</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.3845367972155144</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8284476253675556</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001737434224478984</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4235936999320984</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.240457759343568</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8294113293659923</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007224000497170767</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5306141376495361</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.3845367972155144</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8291166735601518</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003725169602755681</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3843908309936523</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.3845367972155144</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8291379043875328</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001430116723789656</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.456744521856308</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8290514920191364</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.574128984836033e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4681946933269501</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8290598456764119</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.509169298536786e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3186920285224915</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.829053623186806</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.364889654592446e-05</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.38326296210289</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.829046316076014</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.301093358848441e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.3671210110187531</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8290387127121503</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.3767585456371307</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8290328419858461</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3379488289356232</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.829026977189845</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.4329828023910522</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8290212980131367</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.4803788065910339</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8290164167148873</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3882297575473785</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5845367972155147</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8290114955133395</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.5521788001060486</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5845367972155147</v>
+        <v>0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8290114875422451</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.3855109512805939</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.440457759343568</v>
+        <v>0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8290116469641342</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.6559948921203613</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5845367972155147</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8290115513110007</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.3787799477577209</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5845367972155147</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.829011902039157</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3806567788124084</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2713841649125389</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8290116549352287</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4527583122253418</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8290116150797564</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.44974684715271</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8290115513110007</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3834695219993591</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8290116230508509</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.371296226978302</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.3845367972155147</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8290115513110007</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.7116970419883728</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.3845367972155147</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8290116549352287</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4524466097354889</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.5845367972155147</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8290117505883623</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3996460735797882</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2713841649125389</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8290116868196065</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3247120976448059</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8290116469641342</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3014004826545715</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8290116230508509</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3289460837841034</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8290113759469226</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3837673664093018</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8290112962359779</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4129076898097992</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8290113440625446</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.2923675775527954</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8290114636289617</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.3955234587192535</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8290114476867728</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.3523325622081757</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8290114636289617</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4461191296577454</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8290114476867728</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3594285547733307</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.829011503484434</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3111724555492401</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.5845367972155147</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.829011503484434</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.574047327041626</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.5845367972155147</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.829011503484434</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3836362957954407</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.5845367972155147</v>
+        <v>0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8290116549352287</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4988594949245453</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2713841649125389</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8290118701547792</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3458390235900879</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2713841649125389</v>
+        <v>0.16</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8290117824727402</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4591005444526672</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8290117346461734</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.2892290055751801</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8290117824727402</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3515523970127106</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8290115991375675</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3222887516021729</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.829011607108662</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4598231017589569</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8290116150797564</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2935922741889954</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8290116230508509</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3558520972728729</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.5845367972155147</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8290116230508509</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.5259099006652832</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.440457759343568</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8290116629063231</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.5086281895637512</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.440457759343568</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8290117266750789</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.4906811714172363</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.5845367972155147</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8290118382704014</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.345262199640274</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.2713841649125389</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8290118860969681</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3939566612243652</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3845367972155147</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8290118462414958</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.51392662525177</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.3845367972155147</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8290117745016458</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3220374584197998</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.5845367972155147</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8290118940680625</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3186382651329041</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8290117346461734</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3663248121738434</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.829011503484434</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3931518793106079</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8290114556578673</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3640449643135071</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8290114875422451</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3800320327281952</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8290115513110007</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.2512272596359253</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8290115513110007</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.2675151228904724</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8290114716000562</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2703803777694702</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8290113520336391</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.4471275508403778</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8290113121781668</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4472377300262451</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8290114556578673</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3800271451473236</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.16</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8290115911664729</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2428115904331207</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.829011575224284</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.3063474595546722</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8290115513110007</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.279380738735199</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.471384164912539</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8290115114555284</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.2760404646396637</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.5845367972155147</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8290114078313006</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.5661240220069885</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.5845367972155147</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8290112882648835</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3466525077819824</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.5845367972155147</v>
+        <v>0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8290114078313006</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.473209947347641</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.2713841649125389</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8290114556578673</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.2654353380203247</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.2713841649125389</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8290115513110007</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3493951857089996</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.02000000000000013</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8290114317445839</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4326626062393188</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.471384164912539</v>
+        <v>0.02000000000000013</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8290114397156784</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_5_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.4385131001472473</v>
+        <v>0.4385131299495697</v>
       </c>
       <c r="JB2" t="n">
         <v>0.1199999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.3935190737247467</v>
+        <v>0.3935191333293915</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.5799999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.4154058992862701</v>
+        <v>0.4154059588909149</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.4181393384933472</v>
+        <v>0.4181394279003143</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.4399999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.4270336031913757</v>
+        <v>0.4270336627960205</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.4399999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.4721526801586151</v>
+        <v>0.4721527099609375</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.4399999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.3974392116069794</v>
+        <v>0.3974393010139465</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.5799999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.391247570514679</v>
+        <v>0.3912476599216461</v>
       </c>
       <c r="JB12" t="n">
         <v>0.16</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.4019472897052765</v>
+        <v>0.4019473791122437</v>
       </c>
       <c r="JB13" t="n">
         <v>0.16</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.4758819937705994</v>
+        <v>0.4758821129798889</v>
       </c>
       <c r="JB14" t="n">
         <v>0.4399999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.4161631762981415</v>
+        <v>0.4161632359027863</v>
       </c>
       <c r="JB18" t="n">
         <v>0.4399999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.4346599280834198</v>
+        <v>0.4346599578857422</v>
       </c>
       <c r="JB19" t="n">
         <v>0.16</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.4481705129146576</v>
+        <v>0.44817054271698</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.7199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.3911847472190857</v>
+        <v>0.3911848068237305</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.3592920303344727</v>
+        <v>0.3592921197414398</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.8599999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.3486513793468475</v>
+        <v>0.3486514389514923</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.3930076360702515</v>
+        <v>0.3930076956748962</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.3814736306667328</v>
+        <v>0.3814736604690552</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.3849523961544037</v>
+        <v>0.3849524855613708</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.8599999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.4088797867298126</v>
+        <v>0.4088799059391022</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.8599999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.4280325770378113</v>
+        <v>0.4280326664447784</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.7199999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.4205145835876465</v>
+        <v>0.4205146431922913</v>
       </c>
       <c r="JB32" t="n">
         <v>0.16</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.310472697019577</v>
+        <v>0.3104727268218994</v>
       </c>
       <c r="JB33" t="n">
         <v>0.02000000000000007</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.4480330944061279</v>
+        <v>0.4480331838130951</v>
       </c>
       <c r="JB34" t="n">
         <v>0.1600000000000001</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.386787474155426</v>
+        <v>0.3867875337600708</v>
       </c>
       <c r="JB35" t="n">
         <v>0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.4178036749362946</v>
+        <v>0.4178037643432617</v>
       </c>
       <c r="JB36" t="n">
         <v>0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.4168274104595184</v>
+        <v>0.4168274700641632</v>
       </c>
       <c r="JB37" t="n">
         <v>0.4399999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.4596005082130432</v>
+        <v>0.4596005976200104</v>
       </c>
       <c r="JB38" t="n">
         <v>0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.5028281211853027</v>
+        <v>0.5028281807899475</v>
       </c>
       <c r="JB39" t="n">
         <v>0.8599999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.5494162440299988</v>
+        <v>0.5494163036346436</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.6798956990242004</v>
+        <v>0.6798957586288452</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.7971402406692505</v>
+        <v>0.79714035987854</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.02000000000000007</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.1578812301158905</v>
+        <v>0.1578812599182129</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.3</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.7257635593414307</v>
+        <v>0.7257636189460754</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.4399999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.3386078178882599</v>
+        <v>0.3386077582836151</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.4408299624919891</v>
+        <v>0.440829873085022</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.5799999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.5545339584350586</v>
+        <v>0.5545338988304138</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.3</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.4235936999320984</v>
+        <v>0.4235936105251312</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.4399999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.5306141376495361</v>
+        <v>0.5306140184402466</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.4399999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.3843908309936523</v>
+        <v>0.38439080119133</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.7199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.456744521856308</v>
+        <v>0.4567444026470184</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.7199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.4681946933269501</v>
+        <v>0.4681946039199829</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.3186920285224915</v>
+        <v>0.3186918497085571</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.38326296210289</v>
+        <v>0.3832628726959229</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.3671210110187531</v>
+        <v>0.3671208918094635</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.3767585456371307</v>
+        <v>0.3767584264278412</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.3379488289356232</v>
+        <v>0.3379487693309784</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0.5237459518591734</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.4329828023910522</v>
+        <v>0.4329827725887299</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
         <v>0.5237405445165164</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.4803788065910339</v>
+        <v>0.4803787469863892</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0.523735623362795</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.3882297575473785</v>
+        <v>0.3882298469543457</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0.5237356632182673</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.5521788001060486</v>
+        <v>0.5521787405014038</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.3</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC65" t="n">
         <v>0.5237356552471728</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.3855109512805939</v>
+        <v>0.3855108916759491</v>
       </c>
       <c r="JB66" t="n">
         <v>0.16</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.6559948921203613</v>
+        <v>0.6559948325157166</v>
       </c>
       <c r="JB67" t="n">
         <v>0.1600000000000001</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.3787799477577209</v>
+        <v>0.3787798881530762</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.3806567788124084</v>
+        <v>0.3806567192077637</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.1199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.4527583122253418</v>
+        <v>0.4527581930160522</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.44974684715271</v>
+        <v>0.4497467577457428</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.3834695219993591</v>
+        <v>0.3834694027900696</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.371296226978302</v>
+        <v>0.3712961375713348</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.5799999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.7116970419883728</v>
+        <v>0.7116971611976624</v>
       </c>
       <c r="JB74" t="n">
         <v>0.02000000000000007</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.4524466097354889</v>
+        <v>0.4524465501308441</v>
       </c>
       <c r="JB75" t="n">
         <v>0.02000000000000007</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.3996460735797882</v>
+        <v>0.3996460139751434</v>
       </c>
       <c r="JB76" t="n">
         <v>0.02000000000000007</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.3247120976448059</v>
+        <v>0.3247122168540955</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.2599999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.3014004826545715</v>
+        <v>0.3014003932476044</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.3289460837841034</v>
+        <v>0.3289461433887482</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.3837673664093018</v>
+        <v>0.3837674260139465</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.4129076898097992</v>
+        <v>0.4129077792167664</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.2923675775527954</v>
+        <v>0.2923676669597626</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.3955234587192535</v>
+        <v>0.3955235481262207</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.7199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.3523325622081757</v>
+        <v>0.3523326516151428</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.1199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.4461191296577454</v>
+        <v>0.4461192488670349</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.1199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.3594285547733307</v>
+        <v>0.3594286143779755</v>
       </c>
       <c r="JB86" t="n">
         <v>0.16</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.3111724555492401</v>
+        <v>0.3111725747585297</v>
       </c>
       <c r="JB87" t="n">
         <v>0.16</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.574047327041626</v>
+        <v>0.5740472674369812</v>
       </c>
       <c r="JB88" t="n">
         <v>0.1600000000000001</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.3836362957954407</v>
+        <v>0.3836364448070526</v>
       </c>
       <c r="JB89" t="n">
         <v>0.16</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.3458390235900879</v>
+        <v>0.3458389341831207</v>
       </c>
       <c r="JB91" t="n">
         <v>0.16</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.4591005444526672</v>
+        <v>0.4591004550457001</v>
       </c>
       <c r="JB92" t="n">
         <v>0.1600000000000001</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.2892290055751801</v>
+        <v>0.2892289161682129</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.7199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.3515523970127106</v>
+        <v>0.3515525758266449</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.3222887516021729</v>
+        <v>0.3222889006137848</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.4598231017589569</v>
+        <v>0.4598231911659241</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.2935922741889954</v>
+        <v>0.2935923933982849</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.4399999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.3558520972728729</v>
+        <v>0.3558522164821625</v>
       </c>
       <c r="JB98" t="n">
         <v>0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.5259099006652832</v>
+        <v>0.5259098410606384</v>
       </c>
       <c r="JB99" t="n">
         <v>0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.5086281895637512</v>
+        <v>0.5086280703544617</v>
       </c>
       <c r="JB100" t="n">
         <v>0.4399999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.4906811714172363</v>
+        <v>0.4906810224056244</v>
       </c>
       <c r="JB101" t="n">
         <v>0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.345262199640274</v>
+        <v>0.3452620506286621</v>
       </c>
       <c r="JB102" t="n">
         <v>0.3</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.3939566612243652</v>
+        <v>0.3939565420150757</v>
       </c>
       <c r="JB103" t="n">
         <v>0.02000000000000007</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.51392662525177</v>
+        <v>0.5139264464378357</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.8599999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.3220374584197998</v>
+        <v>0.3220373094081879</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.8599999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.3186382651329041</v>
+        <v>0.3186382055282593</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.7199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.3663248121738434</v>
+        <v>0.3663246631622314</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.8599999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.3931518793106079</v>
+        <v>0.3931519985198975</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.8599999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.3640449643135071</v>
+        <v>0.364045113325119</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.8599999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.3800320327281952</v>
+        <v>0.3800321519374847</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.8599999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.2512272596359253</v>
+        <v>0.2512273788452148</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.2675151228904724</v>
+        <v>0.267515242099762</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.7199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.2703803777694702</v>
+        <v>0.270380437374115</v>
       </c>
       <c r="JB113" t="n">
         <v>0.16</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.4471275508403778</v>
+        <v>0.447127640247345</v>
       </c>
       <c r="JB114" t="n">
         <v>0.1600000000000001</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.4472377300262451</v>
+        <v>0.4472378492355347</v>
       </c>
       <c r="JB115" t="n">
         <v>0.1600000000000001</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.3800271451473236</v>
+        <v>0.3800272643566132</v>
       </c>
       <c r="JB116" t="n">
         <v>0.16</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.2428115904331207</v>
+        <v>0.2428116947412491</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.1199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.3063474595546722</v>
+        <v>0.3063475489616394</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.9999999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.279380738735199</v>
+        <v>0.2793808579444885</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.7199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.2760404646396637</v>
+        <v>0.2760404348373413</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.3466525077819824</v>
+        <v>0.346652626991272</v>
       </c>
       <c r="JB122" t="n">
         <v>0.16</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.473209947347641</v>
+        <v>0.4732100665569305</v>
       </c>
       <c r="JB123" t="n">
         <v>0.1600000000000001</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.2654353380203247</v>
+        <v>0.2654354274272919</v>
       </c>
       <c r="JB124" t="n">
         <v>0.02000000000000007</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.3493951857089996</v>
+        <v>0.3493953049182892</v>
       </c>
       <c r="JB125" t="n">
         <v>0.02000000000000013</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.4326626062393188</v>
+        <v>0.4326625168323517</v>
       </c>
       <c r="JB126" t="n">
         <v>0.02000000000000013</v>
